--- a/data/trans_orig/IP36A-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP36A-Provincia-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3457</t>
+          <t>3672</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>794</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6519</t>
+          <t>6395</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1306</t>
+          <t>1342</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7384</t>
+          <t>7416</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,3%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13123</t>
+          <t>12908</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17418</t>
+          <t>17542</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23139</t>
+          <t>23143</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>73,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>33133</t>
+          <t>33101</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>39211</t>
+          <t>39175</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>81,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,69%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1896</t>
+          <t>1878</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9032</t>
+          <t>9230</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6616</t>
+          <t>7185</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4395</t>
+          <t>4441</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13772</t>
+          <t>13030</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>11,94%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>49183</t>
+          <t>48985</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>56319</t>
+          <t>56337</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>84,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>44273</t>
+          <t>43704</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>49599</t>
+          <t>49619</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>95332</t>
+          <t>96074</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>104709</t>
+          <t>104663</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,93%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4790</t>
+          <t>5316</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>633</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5674</t>
+          <t>5698</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1527</t>
+          <t>1894</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7738</t>
+          <t>8451</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>15,43%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20713</t>
+          <t>20187</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>79,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23581</t>
+          <t>23557</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28623</t>
+          <t>28622</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>80,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>47021</t>
+          <t>46308</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>53232</t>
+          <t>52865</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>96,54%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1728</t>
+          <t>1799</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8785</t>
+          <t>8727</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>598</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5664</t>
+          <t>5516</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3565</t>
+          <t>3544</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11626</t>
+          <t>11975</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>22,08%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>20189</t>
+          <t>20247</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>27246</t>
+          <t>27175</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>69,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>19600</t>
+          <t>19748</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>24659</t>
+          <t>24666</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>78,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>42612</t>
+          <t>42263</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>50673</t>
+          <t>50694</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,47%</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4021</t>
+          <t>4168</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4870</t>
+          <t>4447</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>709</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6310</t>
+          <t>6974</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>16,26%</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18512</t>
+          <t>18365</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>81,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15493</t>
+          <t>15916</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>78,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>36586</t>
+          <t>35922</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>42186</t>
+          <t>42187</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,35%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>645</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5955</t>
+          <t>5831</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4138</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1847</t>
+          <t>1781</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7654</t>
+          <t>7596</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>15,95%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>18125</t>
+          <t>18249</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>23440</t>
+          <t>23435</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,27%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>19402</t>
+          <t>19540</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>83,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>39965</t>
+          <t>40023</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>45772</t>
+          <t>45838</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>84,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,26%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>733</t>
+          <t>731</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6753</t>
+          <t>6643</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>643</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6066</t>
+          <t>5694</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2146</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9227</t>
+          <t>9767</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,4%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>52077</t>
+          <t>52187</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>58097</t>
+          <t>58099</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>67114</t>
+          <t>67486</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>72533</t>
+          <t>72537</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>122783</t>
+          <t>122243</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>129990</t>
+          <t>129864</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,37%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1857</t>
+          <t>1848</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8675</t>
+          <t>8886</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3140</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11017</t>
+          <t>10723</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6477</t>
+          <t>6520</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>16805</t>
+          <t>16334</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,01%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>58097</t>
+          <t>57886</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>64915</t>
+          <t>64924</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>58184</t>
+          <t>58478</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>66061</t>
+          <t>65974</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>119169</t>
+          <t>119640</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>129497</t>
+          <t>129454</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,21%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>15541</t>
+          <t>15827</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>30403</t>
+          <t>30572</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>15633</t>
+          <t>15861</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>29705</t>
+          <t>30825</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>35070</t>
+          <t>35680</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>55613</t>
+          <t>55861</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,05%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>271085</t>
+          <t>270916</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>285947</t>
+          <t>285661</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>285925</t>
+          <t>284805</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>299997</t>
+          <t>299769</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>561505</t>
+          <t>561257</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>582048</t>
+          <t>581438</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,22%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4077</t>
+          <t>4116</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11769</t>
+          <t>11687</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>36,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3230</t>
+          <t>3107</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11054</t>
+          <t>10454</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8694</t>
+          <t>8695</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19106</t>
+          <t>19164</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,37%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20494</t>
+          <t>20576</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28186</t>
+          <t>28147</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,52%</t>
+          <t>63,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21943</t>
+          <t>22543</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29767</t>
+          <t>29890</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,5%</t>
+          <t>68,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>46154</t>
+          <t>46096</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>56566</t>
+          <t>56565</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,72%</t>
+          <t>70,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2243</t>
+          <t>2171</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9515</t>
+          <t>9532</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3312</t>
+          <t>3018</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11559</t>
+          <t>11708</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6765</t>
+          <t>6681</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17202</t>
+          <t>16936</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,51%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>43172</t>
+          <t>43155</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>50444</t>
+          <t>50516</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>61089</t>
+          <t>60940</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>69336</t>
+          <t>69630</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>83,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>108133</t>
+          <t>108399</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>118570</t>
+          <t>118654</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,67%</t>
         </is>
       </c>
     </row>
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1350</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7712</t>
+          <t>8350</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1416</t>
+          <t>1407</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8161</t>
+          <t>8219</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,4%</t>
         </is>
       </c>
     </row>
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36573</t>
+          <t>35935</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>42935</t>
+          <t>42297</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>81,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>79294</t>
+          <t>79236</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>86039</t>
+          <t>86048</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,39%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>2597</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9519</t>
+          <t>9515</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>1958</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8611</t>
+          <t>8682</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6018</t>
+          <t>6167</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15482</t>
+          <t>15863</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>19,1%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>32062</t>
+          <t>32066</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>38729</t>
+          <t>38984</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>77,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>32871</t>
+          <t>32800</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>39462</t>
+          <t>39524</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>79,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>67581</t>
+          <t>67200</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>77045</t>
+          <t>76896</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>80,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,58%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>665</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6306</t>
+          <t>5774</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>627</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>5369</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1956</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9081</t>
+          <t>9363</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,66%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22405</t>
+          <t>22937</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28034</t>
+          <t>28046</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>22222</t>
+          <t>22133</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26869</t>
+          <t>26875</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,8%</t>
+          <t>80,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>47132</t>
+          <t>46850</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>54257</t>
+          <t>54225</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>83,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,46%</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2326</t>
+          <t>2485</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>721</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6345</t>
+          <t>5972</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1168</t>
+          <t>1166</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7456</t>
+          <t>6741</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5861,7 +5861,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>9,35%</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>32634</t>
+          <t>32475</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>30824</t>
+          <t>31197</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>36452</t>
+          <t>36448</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,93%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>64673</t>
+          <t>65388</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>70961</t>
+          <t>70963</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,7 +5969,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7505</t>
+          <t>7408</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18722</t>
+          <t>18306</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4453</t>
+          <t>3978</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13097</t>
+          <t>13528</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13174</t>
+          <t>13420</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>26988</t>
+          <t>27345</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,55%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>56938</t>
+          <t>57354</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>68155</t>
+          <t>68252</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>75,26%</t>
+          <t>75,8%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>67010</t>
+          <t>66579</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>75654</t>
+          <t>76129</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>83,11%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>128780</t>
+          <t>128423</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>142594</t>
+          <t>142348</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>82,45%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,38%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2922</t>
+          <t>2630</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10492</t>
+          <t>10419</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>4537</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>13625</t>
+          <t>12976</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>9141</t>
+          <t>8951</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>20180</t>
+          <t>20402</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,42%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>64677</t>
+          <t>64750</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>72247</t>
+          <t>72539</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>63268</t>
+          <t>63917</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>72312</t>
+          <t>72356</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>83,12%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>131881</t>
+          <t>131659</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>142920</t>
+          <t>143110</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,11%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>29687</t>
+          <t>29964</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>48926</t>
+          <t>48322</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>32288</t>
+          <t>32162</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>51979</t>
+          <t>53201</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>67089</t>
+          <t>66616</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>94406</t>
+          <t>95421</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,97%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>335276</t>
+          <t>335880</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>354515</t>
+          <t>354238</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>361104</t>
+          <t>359882</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>380795</t>
+          <t>380921</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>702879</t>
+          <t>701864</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>730196</t>
+          <t>730669</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,03%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,64%</t>
         </is>
       </c>
     </row>
@@ -7384,7 +7384,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3531</t>
+          <t>3166</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2713</t>
+          <t>2873</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9895</t>
+          <t>10205</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3746</t>
+          <t>3548</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12031</t>
+          <t>11540</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,3%</t>
         </is>
       </c>
     </row>
@@ -7492,7 +7492,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27397</t>
+          <t>27762</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22220</t>
+          <t>21910</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29402</t>
+          <t>29242</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>68,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>51012</t>
+          <t>51503</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>59297</t>
+          <t>59495</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>81,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,37%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3777</t>
+          <t>4210</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12424</t>
+          <t>12032</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7055</t>
+          <t>6508</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17181</t>
+          <t>16703</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12439</t>
+          <t>12651</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25638</t>
+          <t>25188</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>17,81%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>55435</t>
+          <t>55827</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>64082</t>
+          <t>63649</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>56395</t>
+          <t>56873</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>66521</t>
+          <t>67068</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,65%</t>
+          <t>77,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>115797</t>
+          <t>116247</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>128996</t>
+          <t>128784</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,05%</t>
         </is>
       </c>
     </row>
@@ -8070,7 +8070,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4313</t>
+          <t>4991</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2139</t>
+          <t>1631</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8286</t>
+          <t>8781</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2877</t>
+          <t>2895</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10979</t>
+          <t>11019</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,71%</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31086</t>
+          <t>30408</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22273</t>
+          <t>21778</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28420</t>
+          <t>28928</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,88%</t>
+          <t>71,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>54979</t>
+          <t>54939</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>63081</t>
+          <t>63063</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,35%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,61%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1742</t>
+          <t>1696</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8205</t>
+          <t>8216</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1498</t>
+          <t>1511</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8580</t>
+          <t>9058</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4797</t>
+          <t>4607</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14813</t>
+          <t>14271</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,18%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>33530</t>
+          <t>33519</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>39993</t>
+          <t>40039</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>80,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>37910</t>
+          <t>37432</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>44992</t>
+          <t>44979</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>80,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>73412</t>
+          <t>73954</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>83428</t>
+          <t>83618</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>83,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,78%</t>
         </is>
       </c>
     </row>
@@ -8756,7 +8756,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5870</t>
+          <t>6011</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4279</t>
+          <t>3790</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7732</t>
+          <t>8106</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,7%</t>
         </is>
       </c>
     </row>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20958</t>
+          <t>20817</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>77,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8899,7 +8899,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20511</t>
+          <t>21000</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>84,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>43886</t>
+          <t>43512</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>50368</t>
+          <t>50343</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>84,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,53%</t>
         </is>
       </c>
     </row>
@@ -9099,7 +9099,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4118</t>
+          <t>4593</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9134,7 +9134,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3932</t>
+          <t>4599</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>626</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5950</t>
+          <t>5913</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,39%</t>
         </is>
       </c>
     </row>
@@ -9207,7 +9207,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>22508</t>
+          <t>22033</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>82,75%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>21363</t>
+          <t>20696</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>81,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>45972</t>
+          <t>46009</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>51279</t>
+          <t>51296</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,79%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2589</t>
+          <t>2562</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9699</t>
+          <t>9725</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8591</t>
+          <t>8088</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19471</t>
+          <t>18716</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>12652</t>
+          <t>12206</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>25882</t>
+          <t>25684</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,31%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>37970</t>
+          <t>37944</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>45080</t>
+          <t>45107</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>79,65%</t>
+          <t>79,6%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>34354</t>
+          <t>35109</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>45234</t>
+          <t>45737</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>63,83%</t>
+          <t>65,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>84,97%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>75612</t>
+          <t>75810</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>88842</t>
+          <t>89288</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>74,5%</t>
+          <t>74,69%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>87,97%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3385</t>
+          <t>3148</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10505</t>
+          <t>10786</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1429</t>
+          <t>1918</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8520</t>
+          <t>8005</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6101</t>
+          <t>6329</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>16175</t>
+          <t>15887</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,09%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>69573</t>
+          <t>69292</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>76693</t>
+          <t>76930</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>86,53%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>68837</t>
+          <t>69352</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>75928</t>
+          <t>75439</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>141260</t>
+          <t>141548</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>151334</t>
+          <t>151106</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>95,98%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>22052</t>
+          <t>22450</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>38235</t>
+          <t>38589</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>34212</t>
+          <t>35004</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>55659</t>
+          <t>55841</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>62753</t>
+          <t>61533</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>89150</t>
+          <t>89457</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,41%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>318887</t>
+          <t>318533</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>335070</t>
+          <t>334672</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,19%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>308348</t>
+          <t>308166</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>329795</t>
+          <t>329003</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>84,66%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>631980</t>
+          <t>631673</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>658377</t>
+          <t>659597</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,47%</t>
         </is>
       </c>
     </row>
@@ -10707,7 +10707,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5596</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10722,7 +10722,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10742,7 +10742,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5116</t>
+          <t>5341</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10757,7 +10757,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>746</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7677</t>
+          <t>7398</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>14,58%</t>
         </is>
       </c>
     </row>
@@ -10815,7 +10815,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22098</t>
+          <t>22392</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -10830,7 +10830,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,8%</t>
+          <t>80,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -10850,7 +10850,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17915</t>
+          <t>17690</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -10865,7 +10865,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>76,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>43049</t>
+          <t>43328</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>49904</t>
+          <t>49980</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,53%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2643</t>
+          <t>2415</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22890</t>
+          <t>24339</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>5473</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15625</t>
+          <t>16301</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9606</t>
+          <t>9326</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33418</t>
+          <t>32471</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,12%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>47052</t>
+          <t>45603</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>67299</t>
+          <t>67527</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>65,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>43690</t>
+          <t>43014</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>54009</t>
+          <t>53842</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,66%</t>
+          <t>72,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>95839</t>
+          <t>96786</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>119651</t>
+          <t>119931</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,15%</t>
+          <t>74,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,78%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2555</t>
+          <t>2537</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8803</t>
+          <t>8829</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,21%</t>
+          <t>42,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2084</t>
+          <t>2119</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8698</t>
+          <t>8283</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5945</t>
+          <t>6301</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15205</t>
+          <t>14714</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>29,8%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12051</t>
+          <t>12025</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18299</t>
+          <t>18317</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>57,79%</t>
+          <t>57,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19831</t>
+          <t>20246</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26445</t>
+          <t>26410</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>70,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>34178</t>
+          <t>34669</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>43438</t>
+          <t>43082</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>70,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>87,24%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>448</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6819</t>
+          <t>6527</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11771,7 +11771,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>5538</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11786,7 +11786,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1351</t>
+          <t>1350</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8592</t>
+          <t>8611</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,38%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>17850</t>
+          <t>18142</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>24208</t>
+          <t>24221</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>73,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,7 +11879,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12619</t>
+          <t>12047</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -11894,7 +11894,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,76%</t>
+          <t>68,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>33662</t>
+          <t>33643</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>40903</t>
+          <t>40904</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>79,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,81%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>531</t>
+          <t>425</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3144</t>
+          <t>3124</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>457</t>
+          <t>478</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3944</t>
+          <t>3941</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,7%</t>
+          <t>55,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1501</t>
+          <t>1422</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5794</t>
+          <t>5808</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>54,34%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>484</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3077</t>
+          <t>3183</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3137</t>
+          <t>3140</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6624</t>
+          <t>6603</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>44,3%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4895</t>
+          <t>4881</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9188</t>
+          <t>9267</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>45,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,95%</t>
+          <t>86,7%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>565</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5467</t>
+          <t>5821</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2255</t>
+          <t>2154</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8355</t>
+          <t>8285</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>39,48%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3619</t>
+          <t>3385</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11230</t>
+          <t>11335</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>25,11%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>18690</t>
+          <t>18336</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>23582</t>
+          <t>23592</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>77,37%</t>
+          <t>75,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>12630</t>
+          <t>12700</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>18730</t>
+          <t>18831</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>60,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>33912</t>
+          <t>33807</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>41523</t>
+          <t>41757</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>74,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>92,5%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3429</t>
+          <t>3314</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11813</t>
+          <t>11788</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4215</t>
+          <t>4125</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14890</t>
+          <t>14991</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9542</t>
+          <t>9341</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>23830</t>
+          <t>23405</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>26,78%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>27497</t>
+          <t>27522</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>35881</t>
+          <t>35996</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>69,95%</t>
+          <t>70,01%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>33203</t>
+          <t>33102</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>43878</t>
+          <t>43968</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>68,83%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>63573</t>
+          <t>63998</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>77861</t>
+          <t>78062</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>72,74%</t>
+          <t>73,22%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>89,31%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5946</t>
+          <t>5751</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15432</t>
+          <t>15806</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>9720</t>
+          <t>9959</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>22230</t>
+          <t>22955</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>43,09%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>18812</t>
+          <t>18513</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>34993</t>
+          <t>34203</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>33,11%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>34612</t>
+          <t>34238</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>44098</t>
+          <t>44293</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>68,41%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>31039</t>
+          <t>30314</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>43549</t>
+          <t>43310</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>58,27%</t>
+          <t>56,91%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>81,75%</t>
+          <t>81,3%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>68320</t>
+          <t>69110</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>84501</t>
+          <t>84800</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>66,89%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>82,08%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>26728</t>
+          <t>28086</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>56756</t>
+          <t>55108</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>38180</t>
+          <t>37838</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>61063</t>
+          <t>60364</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>70319</t>
+          <t>70261</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>109177</t>
+          <t>107481</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,74%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>203522</t>
+          <t>205170</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>233550</t>
+          <t>232192</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>78,83%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>196825</t>
+          <t>197524</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>219708</t>
+          <t>220050</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>76,32%</t>
+          <t>76,59%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>85,33%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>408990</t>
+          <t>410686</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>447848</t>
+          <t>447906</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>79,26%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>86,44%</t>
         </is>
       </c>
     </row>
